--- a/Result/checksun_type/行銷廣告服務.xlsx
+++ b/Result/checksun_type/行銷廣告服務.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>62.0</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>62.09</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>62.7</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>62.09</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>62.7</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>790.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>612.8</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>612.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>798.4</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>937.82</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>937.8200000000001</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-67.06281192221286</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>790</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>790.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>61.84</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>62.06</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>62.74</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>62.06</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>62.74</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>867.4</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>867.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>782.9</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>953.62</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>953.62</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-83.16970658039634</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>5</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>61.9</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>62.07</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>62.78</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>62.07</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>62.78</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>247.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>1127.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>1127.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>839.7</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>965.2</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>965.2</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-19.10206657135859</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>247</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>247.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>62.0</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>62.1</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>62.82</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>62.82</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>1333.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>1180.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>1180.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>835.5</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>965.4</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>965.4</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>47.17677867624377</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>1333</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>1333.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>62.2</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>62.12</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>62.87</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>62.12</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>62.87</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>689.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>1084.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>1084</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>827.2</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>949.2</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>949.2</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>23.81881550581011</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>689</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>689.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>62.32000000000001</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>62.14</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>62.91</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>62.14</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>62.91</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>2063.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>984.0</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>984</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>816.5</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>966.9</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>966.9</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>58.5996247085543</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>2063</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>2063.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>62.56</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>62.18</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>62.96</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>62.18</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>62.96</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>1307.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>698.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>698.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>847.7</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>956.48</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>956.48</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-41.02063445568808</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>1307</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>1307.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>62.66</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>62.17</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>62.99</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>62.17</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>62.99</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>512.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>551.6</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>551.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>760.9</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>959.72</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>959.72</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-100.8702677454739</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>512</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>512.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>62.68000000000001</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>62.17</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>63.01</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>62.17</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>63.01</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>849.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>490.2</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>490.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>740.4</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>969.82</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>969.8200000000001</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-97.58866288282968</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>849</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>849.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>62.56</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>62.15</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>63.02</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>62.15</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>63.02</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>189.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>570.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>570.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>686.3</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>987.48</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>987.48</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-125.5224894046655</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>189</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>189.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>62.54</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>62.14</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>63.06</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>62.14</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>63.06</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>635.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>649.0</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>649</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>830.3</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>1006.9</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>1006.9</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-90.23072409997849</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>635</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>635.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>29.21</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>30.8</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>31.88</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>31.88</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>13046.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>11698.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>11698</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>17294.7</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>34387.42</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>34387.42</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-5549.003271599235</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>13046</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>13046.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>29.02</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>31.04</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>31.93</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>31.04</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>31.93</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>8093.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>11983.4</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>11983.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>18678.8</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>34584.5</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>34584.5</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-5952.775909733751</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>8093</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>8093.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>28.9</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>31.25</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>32.0</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>32</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>10897.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>14504.8</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>14504.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>21270.9</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>34565.74</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>34565.74</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-5786.316253149711</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>10897</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>10897.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>29.01</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>31.5</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>32.08</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>32.08</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>12050.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>18945.4</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>18945.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>25209.1</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>34557.06</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>34557.06</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-5642.291163274313</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>12050</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>12050.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>29.26</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>31.75</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>32.17</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>32.17</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>14404.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>20291.2</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>20291.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>26476.5</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>34460.38</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>34460.38</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-5358.566350478231</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>14404</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>14404.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>29.58</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>32.01</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>32.25</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>32.01</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>32.25</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>14473.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>22891.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>22891.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>26959.7</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>34296.58</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>34296.58</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-5014.082105395319</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>14473</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>14473.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>29.91</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>32.3</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>32.35</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>32.35</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>20700.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>25374.2</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>25374.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>28556.0</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>34314.24</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>34314.24</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-4350.280251512748</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>20700</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>20700.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>30.15</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>32.6</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>32.43</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>32.43</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>33100.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>28037.0</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>28037</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>32710.0</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>34047.14</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>34047.14</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-3913.803308412193</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>33100</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>33100.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>30.32</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>32.91</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>32.49</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>32.91</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>32.49</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>18779.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>31472.8</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>31472.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>38327.3</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>33558.52</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>33558.52</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-4479.057557253822</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>18779</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>18779.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>30.56</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>33.02</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>32.54</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>33.02</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>32.54</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>27405.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>32661.8</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>32661.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>42318.5</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>33657.96</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>33657.96</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-3592.204428554236</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>27405</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>27405.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>30.86</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>33.07</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>32.6</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>33.07</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>32.6</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>26887.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>31028.0</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>31028</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>43724.5</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>33550.22</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>33550.22</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-3121.192657963598</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>26887</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>26887.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>538.2</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>552.05</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>576.4</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>552.05</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>576.4</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>32864382.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>40930647.2</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>40930647.2</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>44524261.4</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>46680868.86</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>46680868.86</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-1953670.607991926</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>32864382</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>32864382.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>533.2</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>552.3</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>577.48</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>552.3</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>577.48</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>46463751.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>36189476.0</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>36189476</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>45465653.4</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>47624299.32</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>47624299.32</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-1355210.902363062</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>46463751</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>46463751.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>530.4</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>553.5</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>578.86</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>553.5</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>578.86</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>12613596.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>43859460.8</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>43859460.8</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>49334872.8</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>50438799.18</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>50438799.18</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-1908943.32638029</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>12613596</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>12613596.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>533.2</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>555.95</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>580.36</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>555.95</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>580.36</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>58932053.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>47741874.4</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>47741874.4</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>50227359.5</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>51664282.3</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>51664282.3</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>994989.2223943844</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>58932053</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>58932053.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>537.8</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>558.85</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>581.72</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>558.85</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>581.72</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>53779454.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>44871115.8</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>44871115.8</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>47583455.9</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>51600106.7</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>51600106.7</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>145237.1412727013</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>53779454</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>53779454.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>539.2</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>561.05</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>582.82</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>561.05</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>582.8200000000001</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>9158526.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>48117875.6</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>48117875.6</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>51575864.2</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>52456694.28</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>52456694.28</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-521817.2653751597</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>9158526</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>9158526.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>544.8</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>563.8</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>584.12</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>563.8</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>584.12</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>84813675.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>54741830.8</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>54741830.8</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>55961046.9</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>53665729.24</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>53665729.24</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>3324697.913177006</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>84813675</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>84813675.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>552.4</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>565.8</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>585.52</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>565.8</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>585.52</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>32025664.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>54810284.8</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>54810284.8</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>50917066.6</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>53133474.32</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>53133474.32</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>595071.5642095059</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>32025664</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>32025664.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>556.4</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>567.35</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>586.7</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>567.35</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>586.7</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>44578260.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>52712844.6</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>52712844.6</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>49263413.2</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>54961949.54</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>54961949.54</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>2330211.116962738</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>44578260</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>44578260.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>560.0</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>568.6</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>587.78</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>568.6</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>587.78</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>70013253.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>50295796.0</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>50295796</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>49903580.7</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>56198727.74</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>56198727.74</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>3380839.081004396</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>70013253</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>70013253.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>564.0</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>569.75</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>589.04</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>569.75</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>589.04</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>42278302.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>55033852.8</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>55033852.8</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>47287033.4</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>56418593.66</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>56418593.66</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>2035814.098170899</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>42278302</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>42278302.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>74.24</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>75.94</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>78.82</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>75.94</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>78.81999999999999</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>709.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>378.4</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>378.4</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>754.4</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>1063.24</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>1063.24</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-65.36342660409002</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>709</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>709.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>74.06</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>76.03</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>78.98</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>76.03</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>78.98</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>384.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>555.6</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>555.6</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>684.0</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>1078.44</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>1078.44</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-81.31309747373018</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>384</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>384.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>74.1</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>76.2</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>79.17</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>79.17</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>189.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>1003.4</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>1003.4</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>665.3</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>1085.84</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>1085.84</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-66.3728738062972</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>189</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>189.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>74.74</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>76.39</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>79.33</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>76.39</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>79.33</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>461.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>997.0</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>997</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>732.8</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>1111.82</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>1111.82</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-21.76638021688211</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>461</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>461.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>75.54</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>76.6</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>79.51</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>79.51000000000001</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>149.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>1109.8</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>1109.8</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>833.5</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>1227.54</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>1227.54</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>13.59169563288503</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>149</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>76.02000000000001</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>76.72</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>79.69</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>76.72</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>79.69</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>1595.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>1130.4</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>1130.4</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>970.4</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>1231.96</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>1231.96</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>97.04638628852092</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>1595</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>1595.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>76.67999999999999</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>76.82</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>79.87</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>76.81999999999999</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>79.87</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>2623.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>812.4</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>812.4</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>872.2</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>1215.96</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>1215.96</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>57.87285914341066</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>2623</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>2623.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>77.26000000000002</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>76.88</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>80.05</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>76.88</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>80.05</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>157.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>327.2</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>327.2</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>724.2</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>1165.2</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>1165.2</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-110.2990674618686</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>157</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>157.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>77.3</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>76.79</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>80.17</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>76.79000000000001</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>80.17</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>1025.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>468.6</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>468.6</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>767.1</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>1165.84</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>1165.84</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-82.39113877434352</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>1025</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>1025.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>77.14000000000001</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>76.71</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>80.29</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>76.70999999999999</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>80.29000000000001</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>252.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>557.2</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>557.2</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>750.8</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>1161.16</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>1161.16</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-132.5801285502242</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>252</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>77.0</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>76.63</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>80.44</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>76.63</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>80.44</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>810.4</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>810.4</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>743.3</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>1172.74</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>1172.74</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-116.7222522104029</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>5</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>172.0</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>173.25</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>175.69</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>173.25</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>175.69</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>7733.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>4697.0</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>4697</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>5851.9</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>6254.16</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>6254.16</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-213.6578208302117</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>7733</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>7733.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>171.7</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>173.4</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>175.78</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>173.4</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>175.78</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>2499.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>3843.4</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>3843.4</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>5698.5</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>6350.88</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>6350.88</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-501.9615915926261</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>2499</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>2499.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>171.7</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>173.58</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>175.93</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>173.58</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>175.93</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>2106.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>4604.2</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>4604.2</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>6779.7</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>6392.4</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>6392.4</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-335.1112072677661</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>2106</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>2106.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>171.8</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>173.75</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>176.05</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>173.75</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>176.05</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>7079.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>5289.6</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>5289.6</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>6948.9</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>6520.9</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>6520.9</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-42.67811511554646</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>7079</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>7079.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>172.1</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>173.98</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>176.23</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>173.98</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>176.23</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>4068.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>6534.6</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>6534.6</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>6326.4</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>6493.66</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>6493.66</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-156.2137650725354</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>4068</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>4068.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>172.4</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>174.18</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>176.39</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>174.18</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>176.39</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>3465.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>7006.8</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>7006.8</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>6196.7</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>6501.12</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>6501.12</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>9.778655170071033</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>3465</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>3465.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>173.0</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>174.4</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>176.56</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>174.4</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>176.56</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>6303.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>7553.6</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>7553.6</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>6534.0</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>6580.28</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>6580.28</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>311.1685892605783</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>6303</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>6303.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>173.0</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>174.52</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>176.72</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>174.52</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>176.72</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>5533.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>8955.2</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>8955.200000000001</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>6264.0</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>6656.86</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>6656.86</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>426.5410454877101</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>5533</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>5533.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>173.3</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>174.7</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>176.84</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>174.7</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>176.84</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>13304.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>8608.2</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>8608.200000000001</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>6084.4</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>6721.58</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>6721.58</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>658.6252313304803</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>13304</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>13304.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>173.7</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>174.88</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>176.96</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>174.88</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>176.96</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>6429.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>6118.2</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>6118.2</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>5270.3</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>6705.14</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>6705.14</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>134.0445957012062</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>6429</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>6429.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>173.9</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>175.02</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>177.08</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>175.02</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>177.08</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>6199.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>5386.6</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>5386.6</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>5295.9</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>6752.54</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>6752.54</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>116.4635235272017</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>6199</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>6199.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>225.8</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>225.6</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>225.17</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>225.6</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>225.17</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>4100097.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>4974669.6</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>4974669.6</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>6354223.3</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>5912736.72</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>5912736.72</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-15971.48970485665</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>4100097</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>4100097.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>225.7</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>225.55</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>225.22</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>225.55</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>225.22</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>6618820.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>5379543.6</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>5379543.6</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>6386712.5</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>5952307.74</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>5952307.74</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>147947.9818177391</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>6618820</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>6618820.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>225.3</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>225.48</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>225.27</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>225.48</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>225.27</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>6203097.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>5813039.0</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>5813039</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>6579924.2</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>5900078.62</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>5900078.62</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>106971.6203565281</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>6203097</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>6203097.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>224.9</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>225.4</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>225.28</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>225.4</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>225.28</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>3520921.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>7520585.8</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>7520585.8</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>6531747.0</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>5884780.7</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>5884780.7</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>89155.29611349385</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>3520921</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>3520921.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>225.5</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>225.42</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>225.36</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>225.42</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>225.36</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>4430413.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>7907031.2</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>7907031.2</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>6365310.4</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>5927338.32</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>5927338.32</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>347895.2866193913</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>4430413</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>4430413.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>225.6</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>225.38</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>225.41</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>225.38</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>225.41</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>6124467.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>7733777.0</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>7733777</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>6073403.1</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>5995710.26</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>5995710.26</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>607653.4413914112</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>6124467</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>6124467.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>226.4</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>225.22</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>225.49</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>225.22</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>225.49</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>8786297.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>7393881.4</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>7393881.4</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>5759668.1</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>5983646.78</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>5983646.78</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>775528.825301745</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>8786297</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>8786297.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>227.2</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>225.15</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>225.57</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>225.15</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>225.57</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>14740831.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>7346809.4</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>7346809.4</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>5225528.1</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>5900102.58</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>5900102.58</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>702457.2728414461</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>14740831</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>14740831.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>227.6</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>225.05</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>225.61</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>225.05</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>225.61</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>5453148.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>5542908.2</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>5542908.2</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>3935777.9</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>5739371.66</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>5739371.66</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-65004.20470331889</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>5453148</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>5453148.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>227.2</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>224.82</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>225.54</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>224.82</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>225.54</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>3564142.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>4823589.6</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>4823589.6</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>3901495.8</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>5822010.16</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>5822010.16</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-163947.2724564346</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>3564142</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>3564142.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>226.8</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>224.62</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>225.49</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>224.62</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>225.49</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>4424989.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>4413029.2</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>4413029.2</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>4057864.5</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>5944404.86</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>5944404.86</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>-97045.75237315614</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>4424989</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>4424989.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>15.37</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>15.13</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>15.22</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>15.22</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>61.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>46.2</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>46.2</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>45.1</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>105.94</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>105.94</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>-4.925024003046232</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>61</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>61.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>15.26</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>15.12</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>15.23</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>15.23</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>16.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>37.0</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>37</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>46.8</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>106.78</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>106.78</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>-6.933128620185634</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>16</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>15.08</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>15.12</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>15.23</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>15.23</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>50.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>65.6</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>65.59999999999999</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>54.3</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>108.72</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>108.72</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>-4.732809193949571</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>50</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>14.92</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>15.12</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>15.22</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>15.22</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>17.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>58.6</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>58.6</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>50.9</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>111.4</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>111.4</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>-5.063323970971275</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>17</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>17.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>14.86</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>15.12</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>15.22</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>15.22</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>87.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>58.4</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>58.4</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>51.4</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>0</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>-1.818940653467592</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>87</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>14.82</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>15.13</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>15.22</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>15.22</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>15.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>44.0</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>44</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>56.1</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>0</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>-4.61914517655277</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>15</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>14.9</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>15.17</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>15.23</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>15.17</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>15.23</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>159.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>56.6</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>56.6</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>67.3</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>0</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>-0.7401821675118612</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>159</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>14.92</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>15.21</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>15.24</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>15.21</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>15.24</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>15.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>43.0</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>43</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>62.9</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>0</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>-10.60094279147086</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>15</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>15.09</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>15.24</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>15.25</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>15.25</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>16.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>43.2</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>43.2</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>62.9</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>0</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>-8.880567154574045</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>16</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>15.22</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>15.25</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>15.27</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>15.27</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>15.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>44.4</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>44.4</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>71.2</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>0</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>-6.212867417772372</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>15</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>15.34</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>15.26</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>15.29</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>15.29</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>78.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>68.2</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>68.2</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>81.2</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>0</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>-2.072836814563829</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>78</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33983,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34167,11 @@
           <t>69.14000000000001</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>70.18</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>71.13</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>70.18000000000001</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>71.13</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34218,16 @@
           <t>154.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>0</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>0</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34244,10 @@
           <t>17.28468721612921</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>154</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34597,11 @@
           <t>69.7</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>70.34</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>71.18</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>70.34</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>71.18000000000001</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34648,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>0</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>0</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34674,10 @@
           <t>41.2126055821771</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>0</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34843,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35027,11 @@
           <t>69.82000000000001</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>70.53</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>71.21</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>70.53</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>71.20999999999999</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35078,16 @@
           <t>436.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>0</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>0</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35104,10 @@
           <t>41.2126055821771</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>436</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>436.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35273,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35457,11 @@
           <t>69.94000000000001</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>70.72</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>71.26</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>70.72</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>71.26000000000001</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35508,16 @@
           <t>527.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>0</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>0</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35534,10 @@
           <t>36.77411383966177</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>527</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>527.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35703,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35887,11 @@
           <t>70.46</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>71.03</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>71.35</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>71.03</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>71.34999999999999</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35938,16 @@
           <t>511.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>0</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>0</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35964,10 @@
           <t>19.37005014179482</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>511</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>511.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36317,11 @@
           <t>70.74</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>71.28</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>71.42</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>71.28</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>71.42</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36368,16 @@
           <t>14.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>0</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>0</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36394,10 @@
           <t>-4.470399788793543</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>14</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36563,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36747,11 @@
           <t>70.72</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>71.35</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>71.45</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>71.34999999999999</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>71.45</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36798,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>0</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>0</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36824,10 @@
           <t>22.6436498210679</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>0</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36993,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37177,11 @@
           <t>70.7</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>71.5</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>71.43</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>71.43000000000001</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37228,16 @@
           <t>179.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>257.0</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>257</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>207.0</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>0</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37254,10 @@
           <t>22.6436498210679</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>179</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>179.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37423,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37607,11 @@
           <t>70.68</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>71.63</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>71.37</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>71.63</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>71.37</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37658,16 @@
           <t>905.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>236.4</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>236.4</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>195.6</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>0</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37684,10 @@
           <t>34.43741684043724</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>905</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>905.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37853,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38037,11 @@
           <t>70.28</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>71.78</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>71.61</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>71.78</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>71.61</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38088,16 @@
           <t>133.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>58.0</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>58</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>124.8</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>0</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38114,10 @@
           <t>-27.72996659047934</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>133</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38283,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38467,11 @@
           <t>69.86</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>71.88</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>71.86</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>71.88</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>71.86</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38518,16 @@
           <t>48.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>93.8</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>93.8</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>143.1</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>0</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38544,10 @@
           <t>-32.8358726849859</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>48</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>48.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
